--- a/data.mn/public/datasets/mrpam-coal-production.xlsx
+++ b/data.mn/public/datasets/mrpam-coal-production.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,49 +414,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>Exports</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>production_kt</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>sales_kt</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>export_kt</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>2021</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>3282.7</v>
       </c>
       <c r="C2" t="n">
         <v>4877.2</v>
@@ -463,16 +460,15 @@
       <c r="D2" t="n">
         <v>4392.1</v>
       </c>
-      <c r="E2" t="n">
-        <v>3282.7</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2021</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>2636.1</v>
       </c>
       <c r="C3" t="n">
         <v>4202.2</v>
@@ -480,16 +476,15 @@
       <c r="D3" t="n">
         <v>3574.1</v>
       </c>
-      <c r="E3" t="n">
-        <v>2636.1</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2021</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2493.1</v>
       </c>
       <c r="C4" t="n">
         <v>3742.7</v>
@@ -497,16 +492,15 @@
       <c r="D4" t="n">
         <v>3359.6</v>
       </c>
-      <c r="E4" t="n">
-        <v>2493.1</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>2021</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>1561.9</v>
       </c>
       <c r="C5" t="n">
         <v>2962.8</v>
@@ -514,16 +508,15 @@
       <c r="D5" t="n">
         <v>2251.7</v>
       </c>
-      <c r="E5" t="n">
-        <v>1561.9</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2021</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>850.4</v>
       </c>
       <c r="C6" t="n">
         <v>2031.4</v>
@@ -531,16 +524,15 @@
       <c r="D6" t="n">
         <v>1425</v>
       </c>
-      <c r="E6" t="n">
-        <v>850.4</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>2021</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>841.5</v>
       </c>
       <c r="C7" t="n">
         <v>1478.9</v>
@@ -548,16 +540,15 @@
       <c r="D7" t="n">
         <v>1432.5</v>
       </c>
-      <c r="E7" t="n">
-        <v>841.5</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>2021</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>1085.2</v>
       </c>
       <c r="C8" t="n">
         <v>1687.1</v>
@@ -565,16 +556,15 @@
       <c r="D8" t="n">
         <v>1597.1</v>
       </c>
-      <c r="E8" t="n">
-        <v>1085.2</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>2021</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>718.1</v>
       </c>
       <c r="C9" t="n">
         <v>1415.2</v>
@@ -582,16 +572,15 @@
       <c r="D9" t="n">
         <v>1431.5</v>
       </c>
-      <c r="E9" t="n">
-        <v>718.1</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>2021</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>562</v>
       </c>
       <c r="C10" t="n">
         <v>1769.8</v>
@@ -599,16 +588,15 @@
       <c r="D10" t="n">
         <v>1421.2</v>
       </c>
-      <c r="E10" t="n">
-        <v>562</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>2021</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>725</v>
       </c>
       <c r="C11" t="n">
         <v>2835.3</v>
@@ -616,16 +604,15 @@
       <c r="D11" t="n">
         <v>1929.9</v>
       </c>
-      <c r="E11" t="n">
-        <v>725</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>2021</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>985.9</v>
       </c>
       <c r="C12" t="n">
         <v>2725.8</v>
@@ -633,16 +620,15 @@
       <c r="D12" t="n">
         <v>2467</v>
       </c>
-      <c r="E12" t="n">
-        <v>985.9</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>2021</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>569</v>
       </c>
       <c r="C13" t="n">
         <v>2583.7</v>
@@ -650,16 +636,15 @@
       <c r="D13" t="n">
         <v>1838</v>
       </c>
-      <c r="E13" t="n">
-        <v>569</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>2022</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>443.1</v>
       </c>
       <c r="C14" t="n">
         <v>2163.5</v>
@@ -667,16 +652,15 @@
       <c r="D14" t="n">
         <v>1636.2</v>
       </c>
-      <c r="E14" t="n">
-        <v>443.1</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>2022</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>503.1</v>
       </c>
       <c r="C15" t="n">
         <v>1626.4</v>
@@ -684,16 +668,15 @@
       <c r="D15" t="n">
         <v>1571.1</v>
       </c>
-      <c r="E15" t="n">
-        <v>503.1</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>2022</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>981.6</v>
       </c>
       <c r="C16" t="n">
         <v>2046.8</v>
@@ -701,16 +684,15 @@
       <c r="D16" t="n">
         <v>1949.1</v>
       </c>
-      <c r="E16" t="n">
-        <v>981.6</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>2022</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>680</v>
       </c>
       <c r="C17" t="n">
         <v>2344.6</v>
@@ -718,16 +700,15 @@
       <c r="D17" t="n">
         <v>1427.2</v>
       </c>
-      <c r="E17" t="n">
-        <v>680</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>2022</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>832.1</v>
       </c>
       <c r="C18" t="n">
         <v>1923.6</v>
@@ -735,16 +716,15 @@
       <c r="D18" t="n">
         <v>1433.9</v>
       </c>
-      <c r="E18" t="n">
-        <v>832.1</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>2022</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>1757.4</v>
       </c>
       <c r="C19" t="n">
         <v>2129.5</v>
@@ -752,16 +732,15 @@
       <c r="D19" t="n">
         <v>2287.1</v>
       </c>
-      <c r="E19" t="n">
-        <v>1757.4</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>2022</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>2434.6</v>
       </c>
       <c r="C20" t="n">
         <v>2304.8</v>
@@ -769,16 +748,15 @@
       <c r="D20" t="n">
         <v>2936.1</v>
       </c>
-      <c r="E20" t="n">
-        <v>2434.6</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>2022</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>3083.2</v>
       </c>
       <c r="C21" t="n">
         <v>3601.9</v>
@@ -786,16 +764,15 @@
       <c r="D21" t="n">
         <v>3821.1</v>
       </c>
-      <c r="E21" t="n">
-        <v>3083.2</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>2022</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>3849.9</v>
       </c>
       <c r="C22" t="n">
         <v>4249.4</v>
@@ -803,16 +780,15 @@
       <c r="D22" t="n">
         <v>4941.4</v>
       </c>
-      <c r="E22" t="n">
-        <v>3849.9</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>2022</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
       </c>
       <c r="B23" t="n">
-        <v>10</v>
+        <v>3954.4</v>
       </c>
       <c r="C23" t="n">
         <v>5128.2</v>
@@ -820,16 +796,15 @@
       <c r="D23" t="n">
         <v>5295.3</v>
       </c>
-      <c r="E23" t="n">
-        <v>3954.4</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>2022</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
       </c>
       <c r="B24" t="n">
-        <v>11</v>
+        <v>4181.5</v>
       </c>
       <c r="C24" t="n">
         <v>5417.9</v>
@@ -837,16 +812,15 @@
       <c r="D24" t="n">
         <v>5530.4</v>
       </c>
-      <c r="E24" t="n">
-        <v>4181.5</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>2022</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
       </c>
       <c r="B25" t="n">
-        <v>12</v>
+        <v>4844.2</v>
       </c>
       <c r="C25" t="n">
         <v>6403.4</v>
@@ -854,16 +828,15 @@
       <c r="D25" t="n">
         <v>6294</v>
       </c>
-      <c r="E25" t="n">
-        <v>4844.2</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>2023</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>4282.4</v>
       </c>
       <c r="C26" t="n">
         <v>5579.1</v>
@@ -871,16 +844,15 @@
       <c r="D26" t="n">
         <v>5759.1</v>
       </c>
-      <c r="E26" t="n">
-        <v>4282.4</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>2023</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>4204.4</v>
       </c>
       <c r="C27" t="n">
         <v>4777</v>
@@ -888,16 +860,15 @@
       <c r="D27" t="n">
         <v>5453.8</v>
       </c>
-      <c r="E27" t="n">
-        <v>4204.4</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>2023</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>5430.4</v>
       </c>
       <c r="C28" t="n">
         <v>6592.1</v>
@@ -905,16 +876,15 @@
       <c r="D28" t="n">
         <v>6653.2</v>
       </c>
-      <c r="E28" t="n">
-        <v>5430.4</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>2023</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>4611</v>
       </c>
       <c r="C29" t="n">
         <v>5791.2</v>
@@ -922,16 +892,15 @@
       <c r="D29" t="n">
         <v>5569</v>
       </c>
-      <c r="E29" t="n">
-        <v>4611</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>2023</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>4152</v>
       </c>
       <c r="C30" t="n">
         <v>5947.7</v>
@@ -939,16 +908,15 @@
       <c r="D30" t="n">
         <v>4894.6</v>
       </c>
-      <c r="E30" t="n">
-        <v>4152</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>2023</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>4113.8</v>
       </c>
       <c r="C31" t="n">
         <v>6195.1</v>
@@ -956,16 +924,15 @@
       <c r="D31" t="n">
         <v>4779.4</v>
       </c>
-      <c r="E31" t="n">
-        <v>4113.8</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>2023</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
       </c>
       <c r="B32" t="n">
-        <v>7</v>
+        <v>5098.1</v>
       </c>
       <c r="C32" t="n">
         <v>5720.8</v>
@@ -973,16 +940,15 @@
       <c r="D32" t="n">
         <v>5827.8</v>
       </c>
-      <c r="E32" t="n">
-        <v>5098.1</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>2023</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
       </c>
       <c r="B33" t="n">
-        <v>8</v>
+        <v>6744.3</v>
       </c>
       <c r="C33" t="n">
         <v>7908.8</v>
@@ -990,16 +956,15 @@
       <c r="D33" t="n">
         <v>7525</v>
       </c>
-      <c r="E33" t="n">
-        <v>6744.3</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>2023</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
       </c>
       <c r="B34" t="n">
-        <v>9</v>
+        <v>6882.5</v>
       </c>
       <c r="C34" t="n">
         <v>8530.5</v>
@@ -1007,16 +972,15 @@
       <c r="D34" t="n">
         <v>7706.1</v>
       </c>
-      <c r="E34" t="n">
-        <v>6882.5</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>2023</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
       </c>
       <c r="B35" t="n">
-        <v>10</v>
+        <v>6712.3</v>
       </c>
       <c r="C35" t="n">
         <v>9090.200000000001</v>
@@ -1024,16 +988,15 @@
       <c r="D35" t="n">
         <v>8022.1</v>
       </c>
-      <c r="E35" t="n">
-        <v>6712.3</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>2023</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
       </c>
       <c r="B36" t="n">
-        <v>11</v>
+        <v>7371.2</v>
       </c>
       <c r="C36" t="n">
         <v>8650.299999999999</v>
@@ -1041,16 +1004,15 @@
       <c r="D36" t="n">
         <v>8835.200000000001</v>
       </c>
-      <c r="E36" t="n">
-        <v>7371.2</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>2023</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
       </c>
       <c r="B37" t="n">
-        <v>12</v>
+        <v>6667.3</v>
       </c>
       <c r="C37" t="n">
         <v>8452</v>
@@ -1058,16 +1020,15 @@
       <c r="D37" t="n">
         <v>8372.4</v>
       </c>
-      <c r="E37" t="n">
-        <v>6667.3</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>2024</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>5385.6</v>
       </c>
       <c r="C38" t="n">
         <v>7072.2</v>
@@ -1075,16 +1036,15 @@
       <c r="D38" t="n">
         <v>6749</v>
       </c>
-      <c r="E38" t="n">
-        <v>5385.6</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>2024</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>4468.2</v>
       </c>
       <c r="C39" t="n">
         <v>7004.3</v>
@@ -1092,16 +1052,15 @@
       <c r="D39" t="n">
         <v>5714.7</v>
       </c>
-      <c r="E39" t="n">
-        <v>4468.2</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>2024</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>6003.1</v>
       </c>
       <c r="C40" t="n">
         <v>8337.299999999999</v>
@@ -1109,16 +1068,15 @@
       <c r="D40" t="n">
         <v>7247</v>
       </c>
-      <c r="E40" t="n">
-        <v>6003.1</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>2024</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
       </c>
       <c r="B41" t="n">
-        <v>4</v>
+        <v>6470.4</v>
       </c>
       <c r="C41" t="n">
         <v>9171.700000000001</v>
@@ -1126,16 +1084,15 @@
       <c r="D41" t="n">
         <v>7512</v>
       </c>
-      <c r="E41" t="n">
-        <v>6470.4</v>
-      </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>2024</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
       </c>
       <c r="B42" t="n">
-        <v>5</v>
+        <v>6649.8</v>
       </c>
       <c r="C42" t="n">
         <v>9148.1</v>
@@ -1143,16 +1100,15 @@
       <c r="D42" t="n">
         <v>7542.4</v>
       </c>
-      <c r="E42" t="n">
-        <v>6649.8</v>
-      </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>2024</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
       </c>
       <c r="B43" t="n">
-        <v>6</v>
+        <v>7010.1</v>
       </c>
       <c r="C43" t="n">
         <v>8883.1</v>
@@ -1160,16 +1116,15 @@
       <c r="D43" t="n">
         <v>7814.4</v>
       </c>
-      <c r="E43" t="n">
-        <v>7010.1</v>
-      </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>2024</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
       </c>
       <c r="B44" t="n">
-        <v>7</v>
+        <v>6892.7</v>
       </c>
       <c r="C44" t="n">
         <v>8629.9</v>
@@ -1177,16 +1132,15 @@
       <c r="D44" t="n">
         <v>7514</v>
       </c>
-      <c r="E44" t="n">
-        <v>6892.7</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>2024</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
       </c>
       <c r="B45" t="n">
-        <v>8</v>
+        <v>6710.9</v>
       </c>
       <c r="C45" t="n">
         <v>8701.4</v>
@@ -1194,16 +1148,15 @@
       <c r="D45" t="n">
         <v>7554.7</v>
       </c>
-      <c r="E45" t="n">
-        <v>6710.9</v>
-      </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
-        <v>2024</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
       </c>
       <c r="B46" t="n">
-        <v>9</v>
+        <v>6075.4</v>
       </c>
       <c r="C46" t="n">
         <v>9363</v>
@@ -1211,16 +1164,15 @@
       <c r="D46" t="n">
         <v>7068.6</v>
       </c>
-      <c r="E46" t="n">
-        <v>6075.4</v>
-      </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
-        <v>2024</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
       </c>
       <c r="B47" t="n">
-        <v>10</v>
+        <v>6828.7</v>
       </c>
       <c r="C47" t="n">
         <v>10268.7</v>
@@ -1228,16 +1180,15 @@
       <c r="D47" t="n">
         <v>8044.3</v>
       </c>
-      <c r="E47" t="n">
-        <v>6828.7</v>
-      </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
-        <v>2024</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
       </c>
       <c r="B48" t="n">
-        <v>11</v>
+        <v>5601.5</v>
       </c>
       <c r="C48" t="n">
         <v>10474.4</v>
@@ -1245,16 +1196,15 @@
       <c r="D48" t="n">
         <v>6997.9</v>
       </c>
-      <c r="E48" t="n">
-        <v>5601.5</v>
-      </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
-        <v>2024</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
       </c>
       <c r="B49" t="n">
-        <v>12</v>
+        <v>6312.8</v>
       </c>
       <c r="C49" t="n">
         <v>9486.799999999999</v>
@@ -1262,16 +1212,15 @@
       <c r="D49" t="n">
         <v>7860.9</v>
       </c>
-      <c r="E49" t="n">
-        <v>6312.8</v>
-      </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v>2025</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>3406.2</v>
       </c>
       <c r="C50" t="n">
         <v>5880.8</v>
@@ -1279,16 +1228,15 @@
       <c r="D50" t="n">
         <v>4693.5</v>
       </c>
-      <c r="E50" t="n">
-        <v>3406.2</v>
-      </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>2025</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>4504.8</v>
       </c>
       <c r="C51" t="n">
         <v>7347.8</v>
@@ -1296,16 +1244,15 @@
       <c r="D51" t="n">
         <v>5456.9</v>
       </c>
-      <c r="E51" t="n">
-        <v>4504.8</v>
-      </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
-        <v>2025</v>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
       </c>
       <c r="B52" t="n">
-        <v>3</v>
+        <v>3897</v>
       </c>
       <c r="C52" t="n">
         <v>7987.8</v>
@@ -1313,16 +1260,15 @@
       <c r="D52" t="n">
         <v>4921.5</v>
       </c>
-      <c r="E52" t="n">
-        <v>3897</v>
-      </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
-        <v>2025</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
       </c>
       <c r="B53" t="n">
-        <v>4</v>
+        <v>7091.4</v>
       </c>
       <c r="C53" t="n">
         <v>8718.299999999999</v>
@@ -1330,16 +1276,15 @@
       <c r="D53" t="n">
         <v>7829.5</v>
       </c>
-      <c r="E53" t="n">
-        <v>7091.4</v>
-      </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
-        <v>2025</v>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
       </c>
       <c r="B54" t="n">
-        <v>5</v>
+        <v>6282.9</v>
       </c>
       <c r="C54" t="n">
         <v>9147.200000000001</v>
@@ -1347,16 +1292,15 @@
       <c r="D54" t="n">
         <v>7025.7</v>
       </c>
-      <c r="E54" t="n">
-        <v>6282.9</v>
-      </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
-        <v>2025</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
       </c>
       <c r="B55" t="n">
-        <v>6</v>
+        <v>4910.1</v>
       </c>
       <c r="C55" t="n">
         <v>6626.1</v>
@@ -1364,16 +1308,15 @@
       <c r="D55" t="n">
         <v>5289.2</v>
       </c>
-      <c r="E55" t="n">
-        <v>4910.1</v>
-      </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
-        <v>2025</v>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
       </c>
       <c r="B56" t="n">
-        <v>7</v>
+        <v>6672</v>
       </c>
       <c r="C56" t="n">
         <v>7981.4</v>
@@ -1381,16 +1324,15 @@
       <c r="D56" t="n">
         <v>7315.1</v>
       </c>
-      <c r="E56" t="n">
-        <v>6672</v>
-      </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
-        <v>2025</v>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
       </c>
       <c r="B57" t="n">
-        <v>8</v>
+        <v>6116.6</v>
       </c>
       <c r="C57" t="n">
         <v>7627.9</v>
@@ -1398,16 +1340,15 @@
       <c r="D57" t="n">
         <v>6783.5</v>
       </c>
-      <c r="E57" t="n">
-        <v>6116.6</v>
-      </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
-        <v>2025</v>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
       </c>
       <c r="B58" t="n">
-        <v>9</v>
+        <v>9100.4</v>
       </c>
       <c r="C58" t="n">
         <v>10130.1</v>
@@ -1415,16 +1356,15 @@
       <c r="D58" t="n">
         <v>10105.3</v>
       </c>
-      <c r="E58" t="n">
-        <v>9100.4</v>
-      </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
-        <v>2025</v>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
       </c>
       <c r="B59" t="n">
-        <v>10</v>
+        <v>7065</v>
       </c>
       <c r="C59" t="n">
         <v>10165.9</v>
@@ -1432,16 +1372,15 @@
       <c r="D59" t="n">
         <v>8382.5</v>
       </c>
-      <c r="E59" t="n">
-        <v>7065</v>
-      </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
-        <v>2025</v>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
       </c>
       <c r="B60" t="n">
-        <v>11</v>
+        <v>8320.799999999999</v>
       </c>
       <c r="C60" t="n">
         <v>11089.8</v>
@@ -1449,16 +1388,15 @@
       <c r="D60" t="n">
         <v>9459.200000000001</v>
       </c>
-      <c r="E60" t="n">
-        <v>8320.799999999999</v>
-      </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
-        <v>2025</v>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
       </c>
       <c r="B61" t="n">
-        <v>12</v>
+        <v>9115.700000000001</v>
       </c>
       <c r="C61" t="n">
         <v>11350.5</v>
@@ -1466,16 +1404,15 @@
       <c r="D61" t="n">
         <v>10503.8</v>
       </c>
-      <c r="E61" t="n">
-        <v>9115.700000000001</v>
-      </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
-        <v>2026</v>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>9306.5</v>
       </c>
       <c r="C62" t="n">
         <v>11398.9</v>
@@ -1483,16 +1420,15 @@
       <c r="D62" t="n">
         <v>10020.3</v>
       </c>
-      <c r="E62" t="n">
-        <v>9306.5</v>
-      </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
-        <v>2026</v>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>6175.3</v>
       </c>
       <c r="C63" t="n">
         <v>9629.299999999999</v>
@@ -1500,16 +1436,15 @@
       <c r="D63" t="n">
         <v>7313.2</v>
       </c>
-      <c r="E63" t="n">
-        <v>6175.3</v>
-      </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
-        <v>2026</v>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>7820.7</v>
       </c>
       <c r="C64" t="n">
         <v>8898.5</v>
@@ -1517,16 +1452,15 @@
       <c r="D64" t="n">
         <v>8695.1</v>
       </c>
-      <c r="E64" t="n">
-        <v>7820.7</v>
-      </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
-        <v>2026</v>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
       </c>
       <c r="B65" t="n">
-        <v>4</v>
+        <v>8878.200000000001</v>
       </c>
       <c r="C65" t="n">
         <v>9890.9</v>
@@ -1534,16 +1468,15 @@
       <c r="D65" t="n">
         <v>9481.200000000001</v>
       </c>
-      <c r="E65" t="n">
-        <v>8878.200000000001</v>
-      </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
-        <v>2026</v>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
       </c>
       <c r="B66" t="n">
-        <v>5</v>
+        <v>8804.799999999999</v>
       </c>
       <c r="C66" t="n">
         <v>12936.9</v>
@@ -1551,16 +1484,15 @@
       <c r="D66" t="n">
         <v>9375.799999999999</v>
       </c>
-      <c r="E66" t="n">
-        <v>8804.799999999999</v>
-      </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
-        <v>2026</v>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
       </c>
       <c r="B67" t="n">
-        <v>6</v>
+        <v>10367.4</v>
       </c>
       <c r="C67" t="n">
         <v>13036</v>
@@ -1568,16 +1500,15 @@
       <c r="D67" t="n">
         <v>11221.5</v>
       </c>
-      <c r="E67" t="n">
-        <v>10367.4</v>
-      </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
-        <v>2026</v>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
       </c>
       <c r="B68" t="n">
-        <v>7</v>
+        <v>8205.700000000001</v>
       </c>
       <c r="C68" t="n">
         <v>11127.8</v>
@@ -1585,7 +1516,1118 @@
       <c r="D68" t="n">
         <v>8761.5</v>
       </c>
-      <c r="E68" t="n">
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>сар</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Борлуулалт</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Олборлолт</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Экспорт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4392.1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4877.2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3282.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3574.1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4202.2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2636.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3359.6</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3742.7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2493.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2251.7</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2962.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1561.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1425</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2031.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>850.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1432.5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1478.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>841.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1597.1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1687.1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1085.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1431.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1415.2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>718.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1421.2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1769.8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1929.9</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2835.3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2467</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2725.8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>985.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1838</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2583.7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1636.2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2163.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>443.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1571.1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1626.4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>503.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1949.1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2046.8</v>
+      </c>
+      <c r="D16" t="n">
+        <v>981.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1427.2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2344.6</v>
+      </c>
+      <c r="D17" t="n">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1433.9</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1923.6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>832.1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2287.1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2129.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1757.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2936.1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2304.8</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2434.6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3821.1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3601.9</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3083.2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4941.4</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4249.4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3849.9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5295.3</v>
+      </c>
+      <c r="C23" t="n">
+        <v>5128.2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3954.4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>5530.4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>5417.9</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4181.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>6294</v>
+      </c>
+      <c r="C25" t="n">
+        <v>6403.4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4844.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5759.1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>5579.1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4282.4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5453.8</v>
+      </c>
+      <c r="C27" t="n">
+        <v>4777</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4204.4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>6653.2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>6592.1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5430.4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>5569</v>
+      </c>
+      <c r="C29" t="n">
+        <v>5791.2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4611</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4894.6</v>
+      </c>
+      <c r="C30" t="n">
+        <v>5947.7</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>4779.4</v>
+      </c>
+      <c r="C31" t="n">
+        <v>6195.1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4113.8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>5827.8</v>
+      </c>
+      <c r="C32" t="n">
+        <v>5720.8</v>
+      </c>
+      <c r="D32" t="n">
+        <v>5098.1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>7525</v>
+      </c>
+      <c r="C33" t="n">
+        <v>7908.8</v>
+      </c>
+      <c r="D33" t="n">
+        <v>6744.3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>7706.1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>8530.5</v>
+      </c>
+      <c r="D34" t="n">
+        <v>6882.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>8022.1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>9090.200000000001</v>
+      </c>
+      <c r="D35" t="n">
+        <v>6712.3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>8835.200000000001</v>
+      </c>
+      <c r="C36" t="n">
+        <v>8650.299999999999</v>
+      </c>
+      <c r="D36" t="n">
+        <v>7371.2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>8372.4</v>
+      </c>
+      <c r="C37" t="n">
+        <v>8452</v>
+      </c>
+      <c r="D37" t="n">
+        <v>6667.3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>6749</v>
+      </c>
+      <c r="C38" t="n">
+        <v>7072.2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>5385.6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5714.7</v>
+      </c>
+      <c r="C39" t="n">
+        <v>7004.3</v>
+      </c>
+      <c r="D39" t="n">
+        <v>4468.2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>7247</v>
+      </c>
+      <c r="C40" t="n">
+        <v>8337.299999999999</v>
+      </c>
+      <c r="D40" t="n">
+        <v>6003.1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>7512</v>
+      </c>
+      <c r="C41" t="n">
+        <v>9171.700000000001</v>
+      </c>
+      <c r="D41" t="n">
+        <v>6470.4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>7542.4</v>
+      </c>
+      <c r="C42" t="n">
+        <v>9148.1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>6649.8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>7814.4</v>
+      </c>
+      <c r="C43" t="n">
+        <v>8883.1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>7010.1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>7514</v>
+      </c>
+      <c r="C44" t="n">
+        <v>8629.9</v>
+      </c>
+      <c r="D44" t="n">
+        <v>6892.7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>7554.7</v>
+      </c>
+      <c r="C45" t="n">
+        <v>8701.4</v>
+      </c>
+      <c r="D45" t="n">
+        <v>6710.9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>7068.6</v>
+      </c>
+      <c r="C46" t="n">
+        <v>9363</v>
+      </c>
+      <c r="D46" t="n">
+        <v>6075.4</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>8044.3</v>
+      </c>
+      <c r="C47" t="n">
+        <v>10268.7</v>
+      </c>
+      <c r="D47" t="n">
+        <v>6828.7</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>6997.9</v>
+      </c>
+      <c r="C48" t="n">
+        <v>10474.4</v>
+      </c>
+      <c r="D48" t="n">
+        <v>5601.5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>7860.9</v>
+      </c>
+      <c r="C49" t="n">
+        <v>9486.799999999999</v>
+      </c>
+      <c r="D49" t="n">
+        <v>6312.8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>4693.5</v>
+      </c>
+      <c r="C50" t="n">
+        <v>5880.8</v>
+      </c>
+      <c r="D50" t="n">
+        <v>3406.2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>5456.9</v>
+      </c>
+      <c r="C51" t="n">
+        <v>7347.8</v>
+      </c>
+      <c r="D51" t="n">
+        <v>4504.8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>4921.5</v>
+      </c>
+      <c r="C52" t="n">
+        <v>7987.8</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3897</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>7829.5</v>
+      </c>
+      <c r="C53" t="n">
+        <v>8718.299999999999</v>
+      </c>
+      <c r="D53" t="n">
+        <v>7091.4</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>7025.7</v>
+      </c>
+      <c r="C54" t="n">
+        <v>9147.200000000001</v>
+      </c>
+      <c r="D54" t="n">
+        <v>6282.9</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>5289.2</v>
+      </c>
+      <c r="C55" t="n">
+        <v>6626.1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>4910.1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>7315.1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>7981.4</v>
+      </c>
+      <c r="D56" t="n">
+        <v>6672</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>6783.5</v>
+      </c>
+      <c r="C57" t="n">
+        <v>7627.9</v>
+      </c>
+      <c r="D57" t="n">
+        <v>6116.6</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>10105.3</v>
+      </c>
+      <c r="C58" t="n">
+        <v>10130.1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>9100.4</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>8382.5</v>
+      </c>
+      <c r="C59" t="n">
+        <v>10165.9</v>
+      </c>
+      <c r="D59" t="n">
+        <v>7065</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>9459.200000000001</v>
+      </c>
+      <c r="C60" t="n">
+        <v>11089.8</v>
+      </c>
+      <c r="D60" t="n">
+        <v>8320.799999999999</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>10503.8</v>
+      </c>
+      <c r="C61" t="n">
+        <v>11350.5</v>
+      </c>
+      <c r="D61" t="n">
+        <v>9115.700000000001</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>10020.3</v>
+      </c>
+      <c r="C62" t="n">
+        <v>11398.9</v>
+      </c>
+      <c r="D62" t="n">
+        <v>9306.5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>7313.2</v>
+      </c>
+      <c r="C63" t="n">
+        <v>9629.299999999999</v>
+      </c>
+      <c r="D63" t="n">
+        <v>6175.3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>8695.1</v>
+      </c>
+      <c r="C64" t="n">
+        <v>8898.5</v>
+      </c>
+      <c r="D64" t="n">
+        <v>7820.7</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>9481.200000000001</v>
+      </c>
+      <c r="C65" t="n">
+        <v>9890.9</v>
+      </c>
+      <c r="D65" t="n">
+        <v>8878.200000000001</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>9375.799999999999</v>
+      </c>
+      <c r="C66" t="n">
+        <v>12936.9</v>
+      </c>
+      <c r="D66" t="n">
+        <v>8804.799999999999</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>11221.5</v>
+      </c>
+      <c r="C67" t="n">
+        <v>13036</v>
+      </c>
+      <c r="D67" t="n">
+        <v>10367.4</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>8761.5</v>
+      </c>
+      <c r="C68" t="n">
+        <v>11127.8</v>
+      </c>
+      <c r="D68" t="n">
         <v>8205.700000000001</v>
       </c>
     </row>

--- a/data.mn/public/datasets/mrpam-coal-production.xlsx
+++ b/data.mn/public/datasets/mrpam-coal-production.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1515,6 +1515,38 @@
       </c>
       <c r="D68" t="n">
         <v>8761.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>8517.5</v>
+      </c>
+      <c r="C69" t="n">
+        <v>12564.6</v>
+      </c>
+      <c r="D69" t="n">
+        <v>9589.1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>6898.3</v>
+      </c>
+      <c r="C70" t="n">
+        <v>12773.5</v>
+      </c>
+      <c r="D70" t="n">
+        <v>8593.9</v>
       </c>
     </row>
   </sheetData>
@@ -1528,7 +1560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2631,6 +2663,38 @@
         <v>8205.700000000001</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>9589.1</v>
+      </c>
+      <c r="C69" t="n">
+        <v>12564.6</v>
+      </c>
+      <c r="D69" t="n">
+        <v>8517.5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>8593.9</v>
+      </c>
+      <c r="C70" t="n">
+        <v>12773.5</v>
+      </c>
+      <c r="D70" t="n">
+        <v>6898.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
